--- a/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
+++ b/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
@@ -810,16 +810,11 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="n">
-        <v>45163.60924099096</v>
+        <v>45216</v>
       </c>
       <c r="F1" s="23" t="n"/>
       <c r="G1" s="23" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="28" t="inlineStr">
         <is>
@@ -855,19 +850,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
@@ -898,8 +880,10 @@
         </is>
       </c>
       <c r="C26" s="26" t="n"/>
-      <c r="D26" s="9" t="n">
-        <v>3000.717</v>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>3450.825</t>
+        </is>
       </c>
       <c r="I26" s="4" t="n"/>
     </row>
@@ -915,8 +899,10 @@
         </is>
       </c>
       <c r="C27" s="26" t="n"/>
-      <c r="D27" s="9" t="n">
-        <v>3755.483</v>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>4318.805</t>
+        </is>
       </c>
       <c r="I27" s="4" t="n"/>
     </row>
@@ -932,8 +918,10 @@
         </is>
       </c>
       <c r="C28" s="26" t="n"/>
-      <c r="D28" s="9" t="n">
-        <v>4887.013</v>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>5620.065</t>
+        </is>
       </c>
       <c r="I28" s="4" t="n"/>
     </row>
@@ -949,8 +937,10 @@
         </is>
       </c>
       <c r="C29" s="26" t="n"/>
-      <c r="D29" s="9" t="n">
-        <v>6905.441</v>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>7941.257</t>
+        </is>
       </c>
       <c r="I29" s="4" t="n"/>
     </row>
@@ -966,8 +956,10 @@
         </is>
       </c>
       <c r="C30" s="26" t="n"/>
-      <c r="D30" s="9" t="n">
-        <v>10177.716</v>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>11704.373</t>
+        </is>
       </c>
       <c r="I30" s="4" t="n"/>
     </row>
@@ -983,8 +975,10 @@
         </is>
       </c>
       <c r="C31" s="26" t="n"/>
-      <c r="D31" s="9" t="n">
-        <v>13994.352</v>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>16093.505</t>
+        </is>
       </c>
       <c r="I31" s="4" t="n"/>
     </row>
@@ -1000,8 +994,10 @@
         </is>
       </c>
       <c r="C32" s="26" t="n"/>
-      <c r="D32" s="19" t="n">
-        <v>17990.825</v>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>20689.449</t>
+        </is>
       </c>
       <c r="I32" s="4" t="n"/>
     </row>
@@ -1035,8 +1031,10 @@
         </is>
       </c>
       <c r="C34" s="26" t="n"/>
-      <c r="D34" s="9" t="n">
-        <v>3000.717</v>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>3450.825</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
@@ -1051,8 +1049,10 @@
         </is>
       </c>
       <c r="C35" s="26" t="n"/>
-      <c r="D35" s="9" t="n">
-        <v>3755.483</v>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>4318.805</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
@@ -1067,8 +1067,10 @@
         </is>
       </c>
       <c r="C36" s="26" t="n"/>
-      <c r="D36" s="9" t="n">
-        <v>4887.013</v>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>5620.065</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
@@ -1083,8 +1085,10 @@
         </is>
       </c>
       <c r="C37" s="26" t="n"/>
-      <c r="D37" s="9" t="n">
-        <v>6905.441</v>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>7941.257</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
@@ -1099,8 +1103,10 @@
         </is>
       </c>
       <c r="C38" s="26" t="n"/>
-      <c r="D38" s="9" t="n">
-        <v>10177.716</v>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>11704.373</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1">
@@ -1115,8 +1121,10 @@
         </is>
       </c>
       <c r="C39" s="26" t="n"/>
-      <c r="D39" s="9" t="n">
-        <v>13994.352</v>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>16093.505</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="19.5" customHeight="1">
@@ -1131,17 +1139,15 @@
         </is>
       </c>
       <c r="C40" s="27" t="n"/>
-      <c r="D40" s="9" t="n">
-        <v>17990.825</v>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42"/>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>20689.449</t>
+        </is>
+      </c>
+    </row>
     <row r="43" ht="20.25" customHeight="1">
       <c r="B43" s="6" t="n"/>
     </row>
-    <row r="44"/>
-    <row r="45"/>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -1168,26 +1174,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
+++ b/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
@@ -810,7 +810,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="n">
-        <v>45216</v>
+        <v>45231</v>
       </c>
       <c r="F1" s="23" t="n"/>
       <c r="G1" s="23" t="n"/>
@@ -880,10 +880,8 @@
         </is>
       </c>
       <c r="C26" s="26" t="n"/>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>3450.825</t>
-        </is>
+      <c r="D26" s="9" t="n">
+        <v>3450.825</v>
       </c>
       <c r="I26" s="4" t="n"/>
     </row>
@@ -899,10 +897,8 @@
         </is>
       </c>
       <c r="C27" s="26" t="n"/>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>4318.805</t>
-        </is>
+      <c r="D27" s="9" t="n">
+        <v>4318.805</v>
       </c>
       <c r="I27" s="4" t="n"/>
     </row>
@@ -918,10 +914,8 @@
         </is>
       </c>
       <c r="C28" s="26" t="n"/>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>5620.065</t>
-        </is>
+      <c r="D28" s="9" t="n">
+        <v>5620.065</v>
       </c>
       <c r="I28" s="4" t="n"/>
     </row>
@@ -937,10 +931,8 @@
         </is>
       </c>
       <c r="C29" s="26" t="n"/>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>7941.257</t>
-        </is>
+      <c r="D29" s="9" t="n">
+        <v>7941.257</v>
       </c>
       <c r="I29" s="4" t="n"/>
     </row>
@@ -956,10 +948,8 @@
         </is>
       </c>
       <c r="C30" s="26" t="n"/>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>11704.373</t>
-        </is>
+      <c r="D30" s="9" t="n">
+        <v>11704.373</v>
       </c>
       <c r="I30" s="4" t="n"/>
     </row>
@@ -975,10 +965,8 @@
         </is>
       </c>
       <c r="C31" s="26" t="n"/>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>16093.505</t>
-        </is>
+      <c r="D31" s="9" t="n">
+        <v>16093.505</v>
       </c>
       <c r="I31" s="4" t="n"/>
     </row>
@@ -994,10 +982,8 @@
         </is>
       </c>
       <c r="C32" s="26" t="n"/>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>20689.449</t>
-        </is>
+      <c r="D32" s="19" t="n">
+        <v>20689.449</v>
       </c>
       <c r="I32" s="4" t="n"/>
     </row>
@@ -1031,10 +1017,8 @@
         </is>
       </c>
       <c r="C34" s="26" t="n"/>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>3450.825</t>
-        </is>
+      <c r="D34" s="9" t="n">
+        <v>3450.825</v>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
@@ -1049,10 +1033,8 @@
         </is>
       </c>
       <c r="C35" s="26" t="n"/>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>4318.805</t>
-        </is>
+      <c r="D35" s="9" t="n">
+        <v>4318.805</v>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
@@ -1067,10 +1049,8 @@
         </is>
       </c>
       <c r="C36" s="26" t="n"/>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>5620.065</t>
-        </is>
+      <c r="D36" s="9" t="n">
+        <v>5620.065</v>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
@@ -1085,10 +1065,8 @@
         </is>
       </c>
       <c r="C37" s="26" t="n"/>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>7941.257</t>
-        </is>
+      <c r="D37" s="9" t="n">
+        <v>7941.257</v>
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
@@ -1103,10 +1081,8 @@
         </is>
       </c>
       <c r="C38" s="26" t="n"/>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>11704.373</t>
-        </is>
+      <c r="D38" s="9" t="n">
+        <v>11704.373</v>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1">
@@ -1121,10 +1097,8 @@
         </is>
       </c>
       <c r="C39" s="26" t="n"/>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>16093.505</t>
-        </is>
+      <c r="D39" s="9" t="n">
+        <v>16093.505</v>
       </c>
     </row>
     <row r="40" ht="19.5" customHeight="1">
@@ -1139,10 +1113,8 @@
         </is>
       </c>
       <c r="C40" s="27" t="n"/>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>20689.449</t>
-        </is>
+      <c r="D40" s="9" t="n">
+        <v>20689.449</v>
       </c>
     </row>
     <row r="43" ht="20.25" customHeight="1">

--- a/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
+++ b/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
@@ -810,7 +810,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="n">
-        <v>45231</v>
+        <v>45232</v>
       </c>
       <c r="F1" s="23" t="n"/>
       <c r="G1" s="23" t="n"/>

--- a/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
+++ b/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
@@ -810,7 +810,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="n">
-        <v>45232</v>
+        <v>45237</v>
       </c>
       <c r="F1" s="23" t="n"/>
       <c r="G1" s="23" t="n"/>

--- a/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
+++ b/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
@@ -810,7 +810,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="F1" s="23" t="n"/>
       <c r="G1" s="23" t="n"/>
@@ -1146,26 +1146,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:E10"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
+++ b/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
@@ -810,7 +810,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="n">
-        <v>45238</v>
+        <v>45244</v>
       </c>
       <c r="F1" s="23" t="n"/>
       <c r="G1" s="23" t="n"/>

--- a/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
+++ b/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
@@ -810,7 +810,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="n">
-        <v>45244</v>
+        <v>45252</v>
       </c>
       <c r="F1" s="23" t="n"/>
       <c r="G1" s="23" t="n"/>
@@ -1146,26 +1146,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
+++ b/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
@@ -810,7 +810,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="n">
-        <v>45252</v>
+        <v>45253</v>
       </c>
       <c r="F1" s="23" t="n"/>
       <c r="G1" s="23" t="n"/>
@@ -1146,26 +1146,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:E10"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
+++ b/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
@@ -810,7 +810,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="F1" s="23" t="n"/>
       <c r="G1" s="23" t="n"/>
@@ -1146,26 +1146,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
+++ b/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
@@ -810,7 +810,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="F1" s="23" t="n"/>
       <c r="G1" s="23" t="n"/>

--- a/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
+++ b/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
@@ -810,7 +810,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="F1" s="23" t="n"/>
       <c r="G1" s="23" t="n"/>

--- a/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
+++ b/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
@@ -810,7 +810,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="F1" s="23" t="n"/>
       <c r="G1" s="23" t="n"/>

--- a/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
+++ b/LISTAS/mi/SOPORTE DE ESTANTE.xlsx
@@ -810,11 +810,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="n">
-        <v>45267</v>
+        <v>45261.57776315277</v>
       </c>
       <c r="F1" s="23" t="n"/>
       <c r="G1" s="23" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="28" t="inlineStr">
         <is>
@@ -850,6 +855,19 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
@@ -881,7 +899,7 @@
       </c>
       <c r="C26" s="26" t="n"/>
       <c r="D26" s="9" t="n">
-        <v>3450.825</v>
+        <v>5282</v>
       </c>
       <c r="I26" s="4" t="n"/>
     </row>
@@ -898,7 +916,7 @@
       </c>
       <c r="C27" s="26" t="n"/>
       <c r="D27" s="9" t="n">
-        <v>4318.805</v>
+        <v>6610.58</v>
       </c>
       <c r="I27" s="4" t="n"/>
     </row>
@@ -915,7 +933,7 @@
       </c>
       <c r="C28" s="26" t="n"/>
       <c r="D28" s="9" t="n">
-        <v>5620.065</v>
+        <v>8602.35</v>
       </c>
       <c r="I28" s="4" t="n"/>
     </row>
@@ -932,7 +950,7 @@
       </c>
       <c r="C29" s="26" t="n"/>
       <c r="D29" s="9" t="n">
-        <v>7941.257</v>
+        <v>12155.28</v>
       </c>
       <c r="I29" s="4" t="n"/>
     </row>
@@ -949,7 +967,7 @@
       </c>
       <c r="C30" s="26" t="n"/>
       <c r="D30" s="9" t="n">
-        <v>11704.373</v>
+        <v>17915.29</v>
       </c>
       <c r="I30" s="4" t="n"/>
     </row>
@@ -966,7 +984,7 @@
       </c>
       <c r="C31" s="26" t="n"/>
       <c r="D31" s="9" t="n">
-        <v>16093.505</v>
+        <v>24633.52</v>
       </c>
       <c r="I31" s="4" t="n"/>
     </row>
@@ -983,7 +1001,7 @@
       </c>
       <c r="C32" s="26" t="n"/>
       <c r="D32" s="19" t="n">
-        <v>20689.449</v>
+        <v>31668.3</v>
       </c>
       <c r="I32" s="4" t="n"/>
     </row>
@@ -1018,7 +1036,7 @@
       </c>
       <c r="C34" s="26" t="n"/>
       <c r="D34" s="9" t="n">
-        <v>3450.825</v>
+        <v>5282</v>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
@@ -1034,7 +1052,7 @@
       </c>
       <c r="C35" s="26" t="n"/>
       <c r="D35" s="9" t="n">
-        <v>4318.805</v>
+        <v>6610.58</v>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
@@ -1050,7 +1068,7 @@
       </c>
       <c r="C36" s="26" t="n"/>
       <c r="D36" s="9" t="n">
-        <v>5620.065</v>
+        <v>8602.35</v>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
@@ -1066,7 +1084,7 @@
       </c>
       <c r="C37" s="26" t="n"/>
       <c r="D37" s="9" t="n">
-        <v>7941.257</v>
+        <v>12155.28</v>
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
@@ -1082,7 +1100,7 @@
       </c>
       <c r="C38" s="26" t="n"/>
       <c r="D38" s="9" t="n">
-        <v>11704.373</v>
+        <v>17915.29</v>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1">
@@ -1098,7 +1116,7 @@
       </c>
       <c r="C39" s="26" t="n"/>
       <c r="D39" s="9" t="n">
-        <v>16093.505</v>
+        <v>24633.52</v>
       </c>
     </row>
     <row r="40" ht="19.5" customHeight="1">
@@ -1114,12 +1132,16 @@
       </c>
       <c r="C40" s="27" t="n"/>
       <c r="D40" s="9" t="n">
-        <v>20689.449</v>
-      </c>
-    </row>
+        <v>31668.3</v>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42"/>
     <row r="43" ht="20.25" customHeight="1">
       <c r="B43" s="6" t="n"/>
     </row>
+    <row r="44"/>
+    <row r="45"/>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -1146,26 +1168,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
